--- a/june-d4a9/June_My_Expressions.xlsx
+++ b/june-d4a9/June_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4404,8 +4404,548 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>I stumbled into ~</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>by pure chance</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>I happened to ~</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>~ wasn't part of the plan</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>one thing led to another</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>enroll in ~ on a whim</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>looking back, ~</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>at the time, ~</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>if I hadn't ~, I'd never have ~</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>~ came out of nowhere</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>put myself in the way of ~</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>make room for ~</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>you can't force ~</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>~ found me</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>go looking for ~</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>leave ~ to chance</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>the harder I chase ~, the ~</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>show up anyway</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>let ~ come to me</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>half hoping ~</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>in hindsight, ~</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>connect the dots</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>~ fell into place</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>make sense of ~</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>read too much into ~</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>turn ~ into a story</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>it only makes sense backwards</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>at random</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>I tell myself ~</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Three Conversations V</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>발표·설명</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>the story I ended up with</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D197"/>
+  <autoFilter ref="A1:D227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>